--- a/ExcelConfig/design/数据配表/模版.xlsx
+++ b/ExcelConfig/design/数据配表/模版.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="20175" tabRatio="417" activeTab="5"/>
+    <workbookView windowWidth="28800" windowHeight="12255" tabRatio="417" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -13,6 +13,7 @@
     <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
     <sheet name="Sheet5" sheetId="5" r:id="rId5"/>
     <sheet name="Sheet6" sheetId="6" r:id="rId6"/>
+    <sheet name="Sheet7" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,6 +36,7 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>MOVPC</author>
+    <author>Fengbin</author>
   </authors>
   <commentList>
     <comment ref="A7" authorId="0">
@@ -199,6 +201,28 @@
           </rPr>
           <t xml:space="preserve">
 必须是有效的Json格式</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M9" authorId="1">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Fengbin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+必须是已存在的文件，目录为输出文件夹</t>
         </r>
       </text>
     </comment>
@@ -1486,8 +1510,44 @@
 </comments>
 </file>
 
+<file path=xl/comments7.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Fengbin</author>
+  </authors>
+  <commentList>
+    <comment ref="D13" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Fengbin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+0 - 单选
+1 - 多选
+2 - 排序
+3 - 量选
+4 - 单项填空</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="634" uniqueCount="141">
   <si>
     <t>## 这一列为特殊列，不会记录到json；只进行转换标记</t>
   </si>
@@ -1574,6 +1634,9 @@
     <t>扩充数据</t>
   </si>
   <si>
+    <t>外部数据</t>
+  </si>
+  <si>
     <t>#type</t>
   </si>
   <si>
@@ -1605,6 +1668,9 @@
   </si>
   <si>
     <t>json</t>
+  </si>
+  <si>
+    <t>insert</t>
   </si>
   <si>
     <t>#group</t>
@@ -1651,6 +1717,9 @@
     <t>可直接输入 json 内容(Json的格式需要一致)</t>
   </si>
   <si>
+    <t>插入文件文本</t>
+  </si>
+  <si>
     <t>一个,老实人</t>
   </si>
   <si>
@@ -1808,6 +1877,102 @@
   </si>
   <si>
     <t>可将表格数据放置到任意指定位置</t>
+  </si>
+  <si>
+    <t>#问卷数据模版，可使用.bat 指定转换为后端可用的 json 文件</t>
+  </si>
+  <si>
+    <t>formId</t>
+  </si>
+  <si>
+    <t>info</t>
+  </si>
+  <si>
+    <t>reward</t>
+  </si>
+  <si>
+    <t>items</t>
+  </si>
+  <si>
+    <t>title</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>表单Id</t>
+  </si>
+  <si>
+    <t>标题</t>
+  </si>
+  <si>
+    <t>介绍</t>
+  </si>
+  <si>
+    <t>邮件奖励道具</t>
+  </si>
+  <si>
+    <t>插入文件</t>
+  </si>
+  <si>
+    <t>你可能喜欢的搜索</t>
+  </si>
+  <si>
+    <t>开发 Google 表单解决方案。 提升 Google 表单体验 使用 插件 插入由您的账号数据或外部服务提供支持的互动内容。</t>
+  </si>
+  <si>
+    <t>100,100,200,300</t>
+  </si>
+  <si>
+    <t>模版_单独输出-Sheet7-选定范围题型.json</t>
+  </si>
+  <si>
+    <t>Id</t>
+  </si>
+  <si>
+    <t>questionType</t>
+  </si>
+  <si>
+    <t>questionItem</t>
+  </si>
+  <si>
+    <t>题目Id</t>
+  </si>
+  <si>
+    <t>题目标题</t>
+  </si>
+  <si>
+    <t>题目类型</t>
+  </si>
+  <si>
+    <t>题目数据</t>
+  </si>
+  <si>
+    <t>单选</t>
+  </si>
+  <si>
+    <t>"红色","蓝色"</t>
+  </si>
+  <si>
+    <t>多选</t>
+  </si>
+  <si>
+    <t>"手枪","散弹","步枪"</t>
+  </si>
+  <si>
+    <t>排序</t>
+  </si>
+  <si>
+    <t>"苹果","香蕉","菠萝","桃子"</t>
+  </si>
+  <si>
+    <t>量选择</t>
+  </si>
+  <si>
+    <t>0,5</t>
+  </si>
+  <si>
+    <t>单项填空</t>
   </si>
 </sst>
 </file>
@@ -1820,14 +1985,8 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="26">
     <font>
-      <sz val="12"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
       <sz val="12"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1838,6 +1997,18 @@
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12.75"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
@@ -1988,12 +2159,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2205,12 +2376,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="26">
+  <borders count="30">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -2419,6 +2605,45 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FFFF0000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFFF0000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color theme="9"/>
+      </left>
+      <right style="thick">
+        <color rgb="FFFF0000"/>
+      </right>
+      <top style="thick">
+        <color theme="9"/>
+      </top>
+      <bottom style="thick">
+        <color theme="9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color rgb="FFFF0000"/>
+      </right>
+      <top style="thick">
+        <color rgb="FFFF0000"/>
+      </top>
+      <bottom style="thick">
+        <color rgb="FFFF0000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
@@ -2544,261 +2769,279 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="21" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="25" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="26" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="23" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="25" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="27" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="25" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2816,85 +3059,97 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3335,6 +3590,11 @@
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext uri="{0b15fc19-7d7d-44ad-8c2d-2c3a37ce22c3}">
+        <chartProps xmlns="https://web.wps.cn/et/2018/main" chartId="{3d45bbc2-caa4-476e-8979-e12aa46b91eb}"/>
+      </c:ext>
+    </c:extLst>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -4447,518 +4707,528 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:N18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="10.0583333333333" style="45" customWidth="1"/>
-    <col min="2" max="4" width="9" style="46"/>
-    <col min="5" max="5" width="26.7916666666667" style="46" customWidth="1"/>
-    <col min="6" max="6" width="15.2916666666667" style="46" customWidth="1"/>
-    <col min="7" max="7" width="12.8083333333333" style="46" customWidth="1"/>
-    <col min="8" max="8" width="9.94166666666667" style="46" customWidth="1"/>
-    <col min="9" max="9" width="27.1416666666667" style="43" customWidth="1"/>
-    <col min="10" max="10" width="19.9916666666667" style="46" customWidth="1"/>
-    <col min="11" max="11" width="19.2166666666667" style="46" customWidth="1"/>
-    <col min="12" max="12" width="53.4333333333333" style="46" customWidth="1"/>
-    <col min="13" max="16384" width="9" style="46"/>
+    <col min="1" max="1" width="10.0583333333333" style="51" customWidth="1"/>
+    <col min="2" max="4" width="9" style="52"/>
+    <col min="5" max="5" width="26.7916666666667" style="52" customWidth="1"/>
+    <col min="6" max="6" width="15.2916666666667" style="52" customWidth="1"/>
+    <col min="7" max="7" width="12.8083333333333" style="52" customWidth="1"/>
+    <col min="8" max="8" width="9.94166666666667" style="52" customWidth="1"/>
+    <col min="9" max="9" width="27.1416666666667" style="49" customWidth="1"/>
+    <col min="10" max="10" width="19.9916666666667" style="52" customWidth="1"/>
+    <col min="11" max="11" width="19.2166666666667" style="52" customWidth="1"/>
+    <col min="12" max="12" width="53.4333333333333" style="52" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="52"/>
   </cols>
   <sheetData>
-    <row r="1" s="41" customFormat="1" spans="1:12">
-      <c r="A1" s="47" t="s">
+    <row r="1" s="47" customFormat="1" spans="1:12">
+      <c r="A1" s="53" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
-      <c r="G1" s="48"/>
-      <c r="H1" s="48"/>
-      <c r="I1" s="69"/>
-      <c r="J1" s="48"/>
-      <c r="K1" s="48"/>
-      <c r="L1" s="70"/>
-    </row>
-    <row r="2" s="41" customFormat="1" spans="1:12">
-      <c r="A2" s="47" t="s">
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="54"/>
+      <c r="G1" s="54"/>
+      <c r="H1" s="54"/>
+      <c r="I1" s="75"/>
+      <c r="J1" s="54"/>
+      <c r="K1" s="54"/>
+      <c r="L1" s="76"/>
+    </row>
+    <row r="2" s="47" customFormat="1" spans="1:12">
+      <c r="A2" s="53" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="48"/>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="69"/>
-      <c r="J2" s="48"/>
-      <c r="K2" s="48"/>
-      <c r="L2" s="70"/>
-    </row>
-    <row r="3" s="41" customFormat="1" spans="1:12">
-      <c r="A3" s="47" t="s">
+      <c r="B2" s="54"/>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="75"/>
+      <c r="J2" s="54"/>
+      <c r="K2" s="54"/>
+      <c r="L2" s="76"/>
+    </row>
+    <row r="3" s="47" customFormat="1" spans="1:12">
+      <c r="A3" s="53" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="48"/>
-      <c r="C3" s="48"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="48"/>
-      <c r="I3" s="69"/>
-      <c r="J3" s="48"/>
-      <c r="K3" s="48"/>
-      <c r="L3" s="70"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="54"/>
+      <c r="E3" s="54"/>
+      <c r="F3" s="54"/>
+      <c r="G3" s="54"/>
+      <c r="H3" s="54"/>
+      <c r="I3" s="75"/>
+      <c r="J3" s="54"/>
+      <c r="K3" s="54"/>
+      <c r="L3" s="76"/>
     </row>
     <row r="4" customFormat="1" spans="1:12">
-      <c r="A4" s="47" t="s">
+      <c r="A4" s="53" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="48"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="48"/>
-      <c r="G4" s="48"/>
-      <c r="H4" s="48"/>
-      <c r="I4" s="69"/>
-      <c r="J4" s="48"/>
-      <c r="K4" s="48"/>
-      <c r="L4" s="70"/>
+      <c r="B4" s="54"/>
+      <c r="C4" s="54"/>
+      <c r="D4" s="54"/>
+      <c r="E4" s="54"/>
+      <c r="F4" s="54"/>
+      <c r="G4" s="54"/>
+      <c r="H4" s="54"/>
+      <c r="I4" s="75"/>
+      <c r="J4" s="54"/>
+      <c r="K4" s="54"/>
+      <c r="L4" s="76"/>
     </row>
     <row r="5" customFormat="1" spans="1:12">
-      <c r="A5" s="47" t="s">
+      <c r="A5" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="48"/>
-      <c r="C5" s="48"/>
-      <c r="D5" s="48"/>
-      <c r="E5" s="48"/>
-      <c r="F5" s="48"/>
-      <c r="G5" s="48"/>
-      <c r="H5" s="48"/>
-      <c r="I5" s="69"/>
-      <c r="J5" s="48"/>
-      <c r="K5" s="48"/>
-      <c r="L5" s="70"/>
-    </row>
-    <row r="6" s="42" customFormat="1" ht="15" spans="1:12">
-      <c r="A6" s="47" t="s">
+      <c r="B5" s="54"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="54"/>
+      <c r="H5" s="54"/>
+      <c r="I5" s="75"/>
+      <c r="J5" s="54"/>
+      <c r="K5" s="54"/>
+      <c r="L5" s="76"/>
+    </row>
+    <row r="6" s="48" customFormat="1" ht="15" spans="1:12">
+      <c r="A6" s="53" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="48"/>
-      <c r="C6" s="48"/>
-      <c r="D6" s="48"/>
-      <c r="E6" s="48"/>
-      <c r="F6" s="48"/>
-      <c r="G6" s="48"/>
-      <c r="H6" s="48"/>
-      <c r="I6" s="48"/>
-      <c r="J6" s="47"/>
-      <c r="K6" s="48"/>
-      <c r="L6" s="70"/>
-    </row>
-    <row r="7" ht="15" spans="1:12">
-      <c r="A7" s="49" t="s">
+      <c r="B6" s="54"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="54"/>
+      <c r="E6" s="54"/>
+      <c r="F6" s="54"/>
+      <c r="G6" s="54"/>
+      <c r="H6" s="54"/>
+      <c r="I6" s="54"/>
+      <c r="J6" s="53"/>
+      <c r="K6" s="54"/>
+      <c r="L6" s="76"/>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="36" t="s">
+      <c r="B7" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="37" t="s">
+      <c r="E7" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="37" t="s">
+      <c r="F7" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="G7" s="50"/>
-      <c r="H7" s="36" t="s">
+      <c r="G7" s="56"/>
+      <c r="H7" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="I7" s="16" t="s">
+      <c r="I7" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="J7" s="2" t="s">
+      <c r="J7" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="K7" s="2" t="s">
+      <c r="K7" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="L7" s="2" t="s">
+      <c r="L7" s="8" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="8" ht="15" spans="1:12">
-      <c r="A8" s="51" t="s">
+    <row r="8" ht="15" spans="1:14">
+      <c r="A8" s="57" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9" t="s">
+      <c r="B8" s="15"/>
+      <c r="C8" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D8" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="E8" s="52" t="s">
+      <c r="E8" s="58" t="s">
         <v>20</v>
       </c>
-      <c r="F8" s="9" t="s">
+      <c r="F8" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="G8" s="53" t="s">
+      <c r="G8" s="59" t="s">
         <v>22</v>
       </c>
-      <c r="H8" s="9" t="s">
+      <c r="H8" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="I8" s="38" t="s">
+      <c r="I8" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="J8" s="71" t="s">
+      <c r="J8" s="77" t="s">
         <v>25</v>
       </c>
-      <c r="K8" s="71" t="s">
+      <c r="K8" s="77" t="s">
         <v>26</v>
       </c>
-      <c r="L8" s="71" t="s">
+      <c r="L8" s="58" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="9" s="43" customFormat="1" ht="34" customHeight="1" spans="1:12">
-      <c r="A9" s="3" t="s">
+      <c r="M8" s="78" t="s">
         <v>28</v>
       </c>
-      <c r="B9" s="38" t="s">
+      <c r="N8" s="79"/>
+    </row>
+    <row r="9" s="49" customFormat="1" ht="34" customHeight="1" spans="1:13">
+      <c r="A9" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="15" t="s">
+      <c r="B9" s="44" t="s">
         <v>30</v>
       </c>
-      <c r="D9" s="39" t="s">
+      <c r="C9" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="E9" s="54" t="s">
+      <c r="D9" s="45" t="s">
         <v>32</v>
       </c>
-      <c r="F9" s="32" t="s">
+      <c r="E9" s="60" t="s">
         <v>33</v>
       </c>
-      <c r="G9" s="32" t="s">
-        <v>32</v>
-      </c>
-      <c r="H9" s="39" t="s">
+      <c r="F9" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="I9" s="40" t="s">
+      <c r="G9" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="H9" s="45" t="s">
         <v>35</v>
       </c>
-      <c r="J9" s="40" t="s">
+      <c r="I9" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="K9" s="40" t="s">
+      <c r="J9" s="46" t="s">
         <v>37</v>
       </c>
-      <c r="L9" s="40" t="s">
+      <c r="K9" s="46" t="s">
         <v>38</v>
       </c>
+      <c r="L9" s="80" t="s">
+        <v>39</v>
+      </c>
+      <c r="M9" s="81" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="10" customFormat="1" ht="15.75" spans="1:12">
-      <c r="A10" s="55" t="s">
-        <v>39</v>
-      </c>
-      <c r="B10" s="56"/>
-      <c r="C10" s="57" t="s">
-        <v>40</v>
-      </c>
-      <c r="D10" s="58" t="s">
-        <v>40</v>
-      </c>
-      <c r="E10" s="59" t="s">
+      <c r="A10" s="61" t="s">
         <v>41</v>
       </c>
-      <c r="F10" s="58" t="s">
+      <c r="B10" s="62"/>
+      <c r="C10" s="63" t="s">
         <v>42</v>
       </c>
-      <c r="G10" s="57" t="s">
-        <v>41</v>
-      </c>
-      <c r="H10" s="58" t="s">
-        <v>40</v>
-      </c>
-      <c r="I10" s="72" t="s">
-        <v>40</v>
-      </c>
-      <c r="J10" s="72" t="s">
-        <v>40</v>
-      </c>
-      <c r="K10" s="72" t="s">
-        <v>40</v>
-      </c>
-      <c r="L10" s="72" t="s">
+      <c r="D10" s="64" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="11" ht="30" spans="1:12">
-      <c r="A11" s="60" t="s">
+      <c r="E10" s="65" t="s">
         <v>43</v>
       </c>
-      <c r="B11" s="61" t="s">
+      <c r="F10" s="64" t="s">
         <v>44</v>
       </c>
-      <c r="C11" s="62" t="s">
+      <c r="G10" s="63" t="s">
+        <v>43</v>
+      </c>
+      <c r="H10" s="64" t="s">
+        <v>42</v>
+      </c>
+      <c r="I10" s="82" t="s">
+        <v>42</v>
+      </c>
+      <c r="J10" s="82" t="s">
+        <v>42</v>
+      </c>
+      <c r="K10" s="82" t="s">
+        <v>42</v>
+      </c>
+      <c r="L10" s="82" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" ht="30" spans="1:13">
+      <c r="A11" s="66" t="s">
         <v>45</v>
       </c>
-      <c r="D11" s="62" t="s">
+      <c r="B11" s="67" t="s">
         <v>46</v>
       </c>
-      <c r="E11" s="63" t="s">
+      <c r="C11" s="68" t="s">
         <v>47</v>
       </c>
-      <c r="F11" s="62" t="s">
+      <c r="D11" s="68" t="s">
         <v>48</v>
       </c>
-      <c r="G11" s="64" t="s">
-        <v>47</v>
-      </c>
-      <c r="H11" s="62" t="s">
+      <c r="E11" s="69" t="s">
         <v>49</v>
       </c>
-      <c r="I11" s="73" t="s">
+      <c r="F11" s="68" t="s">
         <v>50</v>
       </c>
-      <c r="J11" s="73" t="s">
+      <c r="G11" s="70" t="s">
+        <v>49</v>
+      </c>
+      <c r="H11" s="68" t="s">
         <v>51</v>
       </c>
-      <c r="K11" s="73" t="s">
-        <v>51</v>
-      </c>
-      <c r="L11" s="62" t="s">
+      <c r="I11" s="83" t="s">
         <v>52</v>
       </c>
+      <c r="J11" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="K11" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L11" s="68" t="s">
+        <v>54</v>
+      </c>
+      <c r="M11" s="83" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="12" ht="30" spans="1:12">
-      <c r="A12" s="7"/>
-      <c r="B12" s="8">
+      <c r="A12" s="13"/>
+      <c r="B12" s="14">
         <v>1</v>
       </c>
-      <c r="C12" s="9">
+      <c r="C12" s="15">
         <v>0.01</v>
       </c>
-      <c r="D12" s="9">
+      <c r="D12" s="15">
         <v>0.01</v>
       </c>
-      <c r="E12" s="65" t="s">
-        <v>53</v>
-      </c>
-      <c r="F12" s="66" t="s">
-        <v>54</v>
-      </c>
-      <c r="G12" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="H12" s="9" t="s">
+      <c r="E12" s="71" t="s">
         <v>56</v>
       </c>
-      <c r="I12" s="15" t="s">
+      <c r="F12" s="72" t="s">
         <v>57</v>
       </c>
-      <c r="J12" s="9" t="s">
+      <c r="G12" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="K12" s="15" t="s">
+      <c r="H12" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="L12" s="15" t="s">
+      <c r="I12" s="21" t="s">
         <v>60</v>
       </c>
+      <c r="J12" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="K12" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="L12" s="21" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="13" ht="29.25" spans="1:12">
-      <c r="A13" s="10"/>
-      <c r="B13" s="9">
+      <c r="A13" s="16"/>
+      <c r="B13" s="15">
         <v>2</v>
       </c>
-      <c r="C13" s="9">
+      <c r="C13" s="15">
         <v>0.1</v>
       </c>
-      <c r="D13" s="9">
+      <c r="D13" s="15">
         <v>0.1</v>
       </c>
-      <c r="E13" s="65" t="s">
-        <v>61</v>
-      </c>
-      <c r="F13" s="66" t="s">
-        <v>62</v>
-      </c>
-      <c r="G13" s="8" t="s">
+      <c r="E13" s="71" t="s">
+        <v>64</v>
+      </c>
+      <c r="F13" s="72" t="s">
+        <v>65</v>
+      </c>
+      <c r="G13" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="H13" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="I13" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="J13" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="K13" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="L13" s="21" t="s">
         <v>63</v>
       </c>
-      <c r="H13" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="I13" s="15" t="s">
+    </row>
+    <row r="14" ht="28.5" spans="1:12">
+      <c r="A14" s="17"/>
+      <c r="B14" s="15">
+        <v>3</v>
+      </c>
+      <c r="C14" s="15">
+        <v>1</v>
+      </c>
+      <c r="D14" s="15">
+        <v>1</v>
+      </c>
+      <c r="E14" s="71" t="s">
+        <v>71</v>
+      </c>
+      <c r="F14" s="72" t="s">
+        <v>57</v>
+      </c>
+      <c r="G14" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="H14" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="I14" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="J14" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="K14" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="L14" s="21" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="15" ht="29.25" spans="1:12">
+      <c r="A15" s="18"/>
+      <c r="B15" s="15">
+        <v>4</v>
+      </c>
+      <c r="C15" s="15">
+        <v>10</v>
+      </c>
+      <c r="D15" s="15">
+        <v>10</v>
+      </c>
+      <c r="E15" s="71" t="s">
+        <v>76</v>
+      </c>
+      <c r="F15" s="72" t="s">
+        <v>57</v>
+      </c>
+      <c r="G15" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H15" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="I15" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="J15" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="K15" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="L15" s="21" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="16" s="50" customFormat="1" ht="41" customHeight="1" spans="1:12">
+      <c r="A16" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="B16" s="73">
+        <v>5</v>
+      </c>
+      <c r="C16" s="20">
+        <v>100</v>
+      </c>
+      <c r="D16" s="20">
+        <v>100</v>
+      </c>
+      <c r="E16" s="74" t="s">
+        <v>76</v>
+      </c>
+      <c r="F16" s="72" t="s">
         <v>65</v>
       </c>
-      <c r="J13" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="K13" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="L13" s="15" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="14" ht="28.5" spans="1:12">
-      <c r="A14" s="11"/>
-      <c r="B14" s="9">
-        <v>3</v>
-      </c>
-      <c r="C14" s="9">
-        <v>1</v>
-      </c>
-      <c r="D14" s="9">
-        <v>1</v>
-      </c>
-      <c r="E14" s="65" t="s">
-        <v>68</v>
-      </c>
-      <c r="F14" s="66" t="s">
-        <v>54</v>
-      </c>
-      <c r="G14" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="H14" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="I14" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="J14" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="K14" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="L14" s="15" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="15" ht="29.25" spans="1:12">
-      <c r="A15" s="12"/>
-      <c r="B15" s="9">
-        <v>4</v>
-      </c>
-      <c r="C15" s="9">
-        <v>10</v>
-      </c>
-      <c r="D15" s="9">
-        <v>10</v>
-      </c>
-      <c r="E15" s="65" t="s">
-        <v>73</v>
-      </c>
-      <c r="F15" s="66" t="s">
-        <v>54</v>
-      </c>
-      <c r="G15" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H15" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="I15" s="15" t="s">
+      <c r="G16" s="73" t="s">
+        <v>83</v>
+      </c>
+      <c r="H16" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="I16" s="27" t="s">
+        <v>85</v>
+      </c>
+      <c r="J16" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="K16" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="L16" s="28" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="17" ht="41" customHeight="1" spans="1:12">
+      <c r="A17" s="16"/>
+      <c r="B17" s="15">
+        <v>6</v>
+      </c>
+      <c r="C17" s="15">
+        <v>100</v>
+      </c>
+      <c r="D17" s="15">
+        <v>100</v>
+      </c>
+      <c r="E17" s="71" t="s">
         <v>76</v>
       </c>
-      <c r="J15" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="K15" s="15" t="s">
-        <v>78</v>
-      </c>
-      <c r="L15" s="15" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="16" s="44" customFormat="1" ht="41" customHeight="1" spans="1:12">
-      <c r="A16" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="B16" s="67">
-        <v>5</v>
-      </c>
-      <c r="C16" s="14">
-        <v>100</v>
-      </c>
-      <c r="D16" s="14">
-        <v>100</v>
-      </c>
-      <c r="E16" s="68" t="s">
-        <v>73</v>
-      </c>
-      <c r="F16" s="66" t="s">
-        <v>62</v>
-      </c>
-      <c r="G16" s="67" t="s">
-        <v>80</v>
-      </c>
-      <c r="H16" s="14" t="s">
+      <c r="F17" s="72" t="s">
+        <v>57</v>
+      </c>
+      <c r="G17" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="H17" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="I17" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="J17" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="K17" s="21" t="s">
         <v>81</v>
       </c>
-      <c r="I16" s="21" t="s">
-        <v>82</v>
-      </c>
-      <c r="J16" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="K16" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="L16" s="22" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="17" ht="41" customHeight="1" spans="1:12">
-      <c r="A17" s="10"/>
-      <c r="B17" s="9">
-        <v>6</v>
-      </c>
-      <c r="C17" s="9">
-        <v>100</v>
-      </c>
-      <c r="D17" s="9">
-        <v>100</v>
-      </c>
-      <c r="E17" s="65" t="s">
-        <v>73</v>
-      </c>
-      <c r="F17" s="66" t="s">
-        <v>54</v>
-      </c>
-      <c r="G17" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="H17" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="I17" s="15" t="s">
-        <v>82</v>
-      </c>
-      <c r="J17" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K17" s="15" t="s">
-        <v>78</v>
-      </c>
-      <c r="L17" s="23" t="s">
-        <v>60</v>
+      <c r="L17" s="29" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="18" customHeight="1"/>
@@ -4997,271 +5267,271 @@
   </cols>
   <sheetData>
     <row r="1" ht="15.75" spans="1:11">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="36" t="s">
+      <c r="B1" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="37" t="s">
+      <c r="E1" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="28"/>
-      <c r="G1" s="36" t="s">
+      <c r="F1" s="34"/>
+      <c r="G1" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="H1" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="2" ht="30" spans="1:11">
-      <c r="A2" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B2" s="38" t="s">
+      <c r="A2" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="B2" s="44" t="s">
         <v>30</v>
       </c>
-      <c r="D2" s="39" t="s">
+      <c r="C2" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="E2" s="40" t="s">
+      <c r="D2" s="45" t="s">
         <v>32</v>
       </c>
-      <c r="F2" s="32" t="s">
-        <v>32</v>
-      </c>
-      <c r="G2" s="39" t="s">
-        <v>34</v>
-      </c>
-      <c r="H2" s="40" t="s">
+      <c r="E2" s="46" t="s">
+        <v>33</v>
+      </c>
+      <c r="F2" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="G2" s="45" t="s">
         <v>35</v>
       </c>
-      <c r="I2" s="40" t="s">
+      <c r="H2" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="J2" s="40" t="s">
+      <c r="I2" s="46" t="s">
         <v>37</v>
       </c>
-      <c r="K2" s="40" t="s">
+      <c r="J2" s="46" t="s">
         <v>38</v>
       </c>
+      <c r="K2" s="46" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="3" ht="30" spans="1:11">
-      <c r="A3" s="7"/>
-      <c r="B3" s="8">
+      <c r="A3" s="13"/>
+      <c r="B3" s="14">
         <v>10</v>
       </c>
-      <c r="C3" s="9">
+      <c r="C3" s="15">
         <v>0.01</v>
       </c>
-      <c r="D3" s="9">
+      <c r="D3" s="15">
         <v>0.01</v>
       </c>
-      <c r="E3" s="19" t="s">
-        <v>53</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="G3" s="9" t="s">
+      <c r="E3" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="H3" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="I3" s="9" t="s">
+      <c r="F3" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="J3" s="15" t="s">
+      <c r="G3" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="K3" s="15" t="s">
+      <c r="H3" s="21" t="s">
         <v>60</v>
       </c>
+      <c r="I3" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="J3" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="K3" s="21" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="4" ht="29.25" spans="1:11">
-      <c r="A4" s="10"/>
-      <c r="B4" s="8">
+      <c r="A4" s="16"/>
+      <c r="B4" s="14">
         <v>11</v>
       </c>
-      <c r="C4" s="9">
+      <c r="C4" s="15">
         <v>0.1</v>
       </c>
-      <c r="D4" s="9">
+      <c r="D4" s="15">
         <v>0.1</v>
       </c>
-      <c r="E4" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="F4" s="9" t="s">
+      <c r="E4" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="F4" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="G4" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="H4" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="I4" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="J4" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="K4" s="21" t="s">
         <v>63</v>
       </c>
-      <c r="G4" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="H4" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="I4" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="J4" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="K4" s="15" t="s">
-        <v>60</v>
-      </c>
     </row>
     <row r="5" ht="28.5" spans="1:11">
-      <c r="A5" s="11"/>
-      <c r="B5" s="8">
+      <c r="A5" s="17"/>
+      <c r="B5" s="14">
         <v>12</v>
       </c>
-      <c r="C5" s="9">
+      <c r="C5" s="15">
         <v>1</v>
       </c>
-      <c r="D5" s="9">
+      <c r="D5" s="15">
         <v>1</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="E5" s="25" t="s">
+        <v>71</v>
+      </c>
+      <c r="F5" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="G5" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="H5" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="F5" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="H5" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="I5" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="J5" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="K5" s="15" t="s">
-        <v>60</v>
+      <c r="I5" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="J5" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="K5" s="21" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="6" ht="29.25" spans="1:11">
-      <c r="A6" s="12"/>
-      <c r="B6" s="8">
+      <c r="A6" s="18"/>
+      <c r="B6" s="14">
         <v>13</v>
       </c>
-      <c r="C6" s="9">
+      <c r="C6" s="15">
         <v>10</v>
       </c>
-      <c r="D6" s="9">
+      <c r="D6" s="15">
         <v>10</v>
       </c>
-      <c r="E6" s="19" t="s">
-        <v>73</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="G6" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="H6" s="15" t="s">
+      <c r="E6" s="25" t="s">
         <v>76</v>
       </c>
-      <c r="I6" s="9" t="s">
+      <c r="F6" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="J6" s="15" t="s">
+      <c r="G6" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="K6" s="15" t="s">
-        <v>60</v>
+      <c r="H6" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="I6" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="J6" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="K6" s="21" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="7" ht="28.5" spans="1:11">
-      <c r="A7" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="B7" s="8">
+      <c r="A7" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="B7" s="14">
         <v>14</v>
       </c>
-      <c r="C7" s="14">
+      <c r="C7" s="20">
         <v>100</v>
       </c>
-      <c r="D7" s="14">
+      <c r="D7" s="20">
         <v>100</v>
       </c>
-      <c r="E7" s="20" t="s">
-        <v>73</v>
-      </c>
-      <c r="F7" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="G7" s="14" t="s">
+      <c r="E7" s="26" t="s">
+        <v>76</v>
+      </c>
+      <c r="F7" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="G7" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="H7" s="27" t="s">
+        <v>85</v>
+      </c>
+      <c r="I7" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="J7" s="27" t="s">
         <v>81</v>
       </c>
-      <c r="H7" s="21" t="s">
-        <v>82</v>
-      </c>
-      <c r="I7" s="14" t="s">
+      <c r="K7" s="28" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="8" ht="27.75" spans="1:11">
+      <c r="A8" s="16"/>
+      <c r="B8" s="14">
+        <v>15</v>
+      </c>
+      <c r="C8" s="15">
+        <v>100</v>
+      </c>
+      <c r="D8" s="15">
+        <v>100</v>
+      </c>
+      <c r="E8" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="F8" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="J7" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="K7" s="22" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="8" ht="27.75" spans="1:11">
-      <c r="A8" s="10"/>
-      <c r="B8" s="8">
-        <v>15</v>
-      </c>
-      <c r="C8" s="9">
-        <v>100</v>
-      </c>
-      <c r="D8" s="9">
-        <v>100</v>
-      </c>
-      <c r="E8" s="19" t="s">
-        <v>73</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="G8" s="9" t="s">
+      <c r="G8" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="H8" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="I8" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="J8" s="21" t="s">
         <v>81</v>
       </c>
-      <c r="H8" s="15" t="s">
-        <v>82</v>
-      </c>
-      <c r="I8" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="J8" s="15" t="s">
-        <v>78</v>
-      </c>
-      <c r="K8" s="23" t="s">
-        <v>60</v>
+      <c r="K8" s="29" t="s">
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -5292,215 +5562,215 @@
   </cols>
   <sheetData>
     <row r="1" ht="15.75" spans="1:10">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="36" t="s">
+      <c r="B1" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="37" t="s">
+      <c r="E1" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="28"/>
-      <c r="G1" s="36" t="s">
+      <c r="F1" s="34"/>
+      <c r="G1" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="H1" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="8" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="2" ht="15.75" spans="1:10">
-      <c r="A2" s="7"/>
-      <c r="B2" s="8">
+      <c r="A2" s="13"/>
+      <c r="B2" s="14">
         <v>20</v>
       </c>
-      <c r="C2" s="9">
+      <c r="C2" s="15">
         <v>0.01</v>
       </c>
-      <c r="D2" s="9">
+      <c r="D2" s="15">
         <v>0.01</v>
       </c>
-      <c r="E2" s="19" t="s">
-        <v>53</v>
-      </c>
-      <c r="F2" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="G2" s="9" t="s">
+      <c r="E2" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="H2" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="I2" s="9" t="s">
+      <c r="F2" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="J2" s="15" t="s">
+      <c r="G2" s="15" t="s">
         <v>59</v>
       </c>
+      <c r="H2" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="I2" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="J2" s="21" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="3" ht="15" spans="1:10">
-      <c r="A3" s="10"/>
-      <c r="B3" s="8">
+      <c r="A3" s="16"/>
+      <c r="B3" s="14">
         <v>21</v>
       </c>
-      <c r="C3" s="9">
+      <c r="C3" s="15">
         <v>0.1</v>
       </c>
-      <c r="D3" s="9">
+      <c r="D3" s="15">
         <v>0.1</v>
       </c>
-      <c r="E3" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="G3" s="9" t="s">
+      <c r="E3" s="25" t="s">
         <v>64</v>
       </c>
-      <c r="H3" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="I3" s="9" t="s">
+      <c r="F3" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="J3" s="15" t="s">
+      <c r="G3" s="15" t="s">
         <v>67</v>
       </c>
+      <c r="H3" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="I3" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="J3" s="21" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="11"/>
-      <c r="B4" s="8">
+      <c r="A4" s="17"/>
+      <c r="B4" s="14">
         <v>22</v>
       </c>
-      <c r="C4" s="9">
+      <c r="C4" s="15">
         <v>1</v>
       </c>
-      <c r="D4" s="9">
+      <c r="D4" s="15">
         <v>1</v>
       </c>
-      <c r="E4" s="19" t="s">
+      <c r="E4" s="25" t="s">
+        <v>71</v>
+      </c>
+      <c r="F4" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="G4" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="H4" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="F4" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="H4" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="I4" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="J4" s="15" t="s">
-        <v>72</v>
+      <c r="I4" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="J4" s="21" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="5" ht="15" spans="1:10">
-      <c r="A5" s="12"/>
-      <c r="B5" s="8">
+      <c r="A5" s="18"/>
+      <c r="B5" s="14">
         <v>23</v>
       </c>
-      <c r="C5" s="9">
+      <c r="C5" s="15">
         <v>10</v>
       </c>
-      <c r="D5" s="9">
+      <c r="D5" s="15">
         <v>10</v>
       </c>
-      <c r="E5" s="19" t="s">
-        <v>73</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="H5" s="15" t="s">
+      <c r="E5" s="25" t="s">
         <v>76</v>
       </c>
-      <c r="I5" s="9" t="s">
+      <c r="F5" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="J5" s="15" t="s">
+      <c r="G5" s="15" t="s">
         <v>78</v>
       </c>
+      <c r="H5" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="I5" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="J5" s="21" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="6" ht="15.75" spans="1:10">
-      <c r="A6" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="B6" s="8">
+      <c r="A6" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="B6" s="14">
         <v>24</v>
       </c>
-      <c r="C6" s="14">
+      <c r="C6" s="20">
         <v>100</v>
       </c>
-      <c r="D6" s="14">
+      <c r="D6" s="20">
         <v>100</v>
       </c>
-      <c r="E6" s="20" t="s">
-        <v>73</v>
-      </c>
-      <c r="F6" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="G6" s="14" t="s">
+      <c r="E6" s="26" t="s">
+        <v>76</v>
+      </c>
+      <c r="F6" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="G6" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="H6" s="27" t="s">
+        <v>85</v>
+      </c>
+      <c r="I6" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="J6" s="27" t="s">
         <v>81</v>
       </c>
-      <c r="H6" s="21" t="s">
-        <v>82</v>
-      </c>
-      <c r="I6" s="14" t="s">
+    </row>
+    <row r="7" ht="15" spans="1:10">
+      <c r="A7" s="16"/>
+      <c r="B7" s="14">
+        <v>25</v>
+      </c>
+      <c r="C7" s="15">
+        <v>100</v>
+      </c>
+      <c r="D7" s="15">
+        <v>100</v>
+      </c>
+      <c r="E7" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="F7" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="J6" s="21" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="7" ht="15" spans="1:10">
-      <c r="A7" s="10"/>
-      <c r="B7" s="8">
-        <v>25</v>
-      </c>
-      <c r="C7" s="9">
-        <v>100</v>
-      </c>
-      <c r="D7" s="9">
-        <v>100</v>
-      </c>
-      <c r="E7" s="19" t="s">
-        <v>73</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="G7" s="9" t="s">
+      <c r="G7" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="H7" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="I7" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="J7" s="21" t="s">
         <v>81</v>
-      </c>
-      <c r="H7" s="15" t="s">
-        <v>82</v>
-      </c>
-      <c r="I7" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="J7" s="15" t="s">
-        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -5529,261 +5799,261 @@
   </cols>
   <sheetData>
     <row r="1" ht="15.75" spans="1:11">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="25" t="s">
+      <c r="B1" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="26" t="s">
+      <c r="C1" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="26" t="s">
+      <c r="D1" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="27" t="s">
+      <c r="E1" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="28"/>
-      <c r="G1" s="25" t="s">
+      <c r="F1" s="34"/>
+      <c r="G1" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="H1" s="28"/>
-      <c r="I1" s="2" t="s">
+      <c r="H1" s="34"/>
+      <c r="I1" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="J1" s="28"/>
-      <c r="K1" s="2" t="s">
+      <c r="J1" s="34"/>
+      <c r="K1" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="2" ht="15.75" spans="1:11">
-      <c r="A2" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="B2" s="30" t="s">
-        <v>84</v>
-      </c>
-      <c r="C2" s="30" t="s">
-        <v>84</v>
-      </c>
-      <c r="D2" s="30" t="s">
-        <v>84</v>
-      </c>
-      <c r="E2" s="30" t="s">
-        <v>84</v>
-      </c>
-      <c r="F2" s="31"/>
-      <c r="G2" s="30" t="s">
-        <v>84</v>
-      </c>
-      <c r="H2" s="32"/>
-      <c r="I2" s="30" t="s">
-        <v>84</v>
-      </c>
-      <c r="J2" s="15"/>
-      <c r="K2" s="30" t="s">
-        <v>84</v>
+      <c r="A2" s="35" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="C2" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="D2" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="E2" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="F2" s="37"/>
+      <c r="G2" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="H2" s="38"/>
+      <c r="I2" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="J2" s="21"/>
+      <c r="K2" s="36" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="3" ht="30" spans="1:11">
-      <c r="A3" s="7"/>
-      <c r="B3" s="33">
+      <c r="A3" s="13"/>
+      <c r="B3" s="39">
         <v>10</v>
       </c>
-      <c r="C3" s="34">
+      <c r="C3" s="40">
         <v>0.01</v>
       </c>
-      <c r="D3" s="34">
+      <c r="D3" s="40">
         <v>0.01</v>
       </c>
-      <c r="E3" s="35" t="s">
+      <c r="E3" s="41" t="s">
+        <v>88</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="G3" s="40" t="s">
+        <v>89</v>
+      </c>
+      <c r="H3" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="I3" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="J3" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="K3" s="21" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="4" ht="29.25" spans="1:11">
+      <c r="A4" s="16"/>
+      <c r="B4" s="14">
+        <v>11</v>
+      </c>
+      <c r="C4" s="15">
+        <v>0.1</v>
+      </c>
+      <c r="D4" s="15">
+        <v>0.1</v>
+      </c>
+      <c r="E4" s="25" t="s">
+        <v>91</v>
+      </c>
+      <c r="F4" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="G4" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="H4" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="I4" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="J4" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="K4" s="21" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="5" ht="28.5" spans="1:11">
+      <c r="A5" s="17"/>
+      <c r="B5" s="14">
+        <v>12</v>
+      </c>
+      <c r="C5" s="15">
+        <v>1</v>
+      </c>
+      <c r="D5" s="15">
+        <v>1</v>
+      </c>
+      <c r="E5" s="25" t="s">
+        <v>94</v>
+      </c>
+      <c r="F5" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="G5" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="H5" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="I5" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="J5" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="K5" s="21" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="6" ht="29.25" spans="1:11">
+      <c r="A6" s="18"/>
+      <c r="B6" s="14">
+        <v>13</v>
+      </c>
+      <c r="C6" s="15">
+        <v>10</v>
+      </c>
+      <c r="D6" s="15">
+        <v>10</v>
+      </c>
+      <c r="E6" s="25" t="s">
+        <v>97</v>
+      </c>
+      <c r="F6" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="G6" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="H6" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="I6" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="J6" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="K6" s="21" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="7" ht="28.5" spans="1:11">
+      <c r="A7" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="B7" s="14">
+        <v>14</v>
+      </c>
+      <c r="C7" s="20">
+        <v>100</v>
+      </c>
+      <c r="D7" s="20">
+        <v>100</v>
+      </c>
+      <c r="E7" s="25" t="s">
+        <v>97</v>
+      </c>
+      <c r="F7" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="G7" s="20" t="s">
+        <v>100</v>
+      </c>
+      <c r="H7" s="27" t="s">
         <v>85</v>
       </c>
-      <c r="F3" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="G3" s="34" t="s">
-        <v>86</v>
-      </c>
-      <c r="H3" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="I3" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="J3" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="K3" s="15" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="4" ht="29.25" spans="1:11">
-      <c r="A4" s="10"/>
-      <c r="B4" s="8">
-        <v>11</v>
-      </c>
-      <c r="C4" s="9">
-        <v>0.1</v>
-      </c>
-      <c r="D4" s="9">
-        <v>0.1</v>
-      </c>
-      <c r="E4" s="19" t="s">
-        <v>88</v>
-      </c>
-      <c r="F4" s="9" t="s">
+      <c r="I7" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="J7" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="K7" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="G4" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="H4" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="I4" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="J4" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="K4" s="15" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="5" ht="28.5" spans="1:11">
-      <c r="A5" s="11"/>
-      <c r="B5" s="8">
-        <v>12</v>
-      </c>
-      <c r="C5" s="9">
-        <v>1</v>
-      </c>
-      <c r="D5" s="9">
-        <v>1</v>
-      </c>
-      <c r="E5" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="H5" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="I5" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="J5" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="K5" s="15" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="6" ht="29.25" spans="1:11">
-      <c r="A6" s="12"/>
-      <c r="B6" s="8">
-        <v>13</v>
-      </c>
-      <c r="C6" s="9">
-        <v>10</v>
-      </c>
-      <c r="D6" s="9">
-        <v>10</v>
-      </c>
-      <c r="E6" s="19" t="s">
-        <v>94</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="G6" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="H6" s="15" t="s">
-        <v>76</v>
-      </c>
-      <c r="I6" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="J6" s="15" t="s">
-        <v>78</v>
-      </c>
-      <c r="K6" s="15" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="7" ht="28.5" spans="1:11">
-      <c r="A7" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="B7" s="8">
-        <v>14</v>
-      </c>
-      <c r="C7" s="14">
+    </row>
+    <row r="8" ht="27.75" spans="1:11">
+      <c r="A8" s="16"/>
+      <c r="B8" s="14">
+        <v>15</v>
+      </c>
+      <c r="C8" s="15">
         <v>100</v>
       </c>
-      <c r="D7" s="14">
+      <c r="D8" s="15">
         <v>100</v>
       </c>
-      <c r="E7" s="19" t="s">
-        <v>94</v>
-      </c>
-      <c r="F7" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="G7" s="14" t="s">
+      <c r="E8" s="25" t="s">
         <v>97</v>
       </c>
-      <c r="H7" s="21" t="s">
-        <v>82</v>
-      </c>
-      <c r="I7" s="14" t="s">
-        <v>98</v>
-      </c>
-      <c r="J7" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="K7" s="22" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="8" ht="27.75" spans="1:11">
-      <c r="A8" s="10"/>
-      <c r="B8" s="8">
-        <v>15</v>
-      </c>
-      <c r="C8" s="9">
+      <c r="F8" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="G8" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="D8" s="9">
-        <v>100</v>
-      </c>
-      <c r="E8" s="19" t="s">
-        <v>94</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="G8" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="H8" s="15" t="s">
-        <v>82</v>
-      </c>
-      <c r="I8" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="J8" s="15" t="s">
-        <v>78</v>
-      </c>
-      <c r="K8" s="23" t="s">
-        <v>60</v>
+      <c r="H8" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="I8" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="J8" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="K8" s="29" t="s">
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -5814,681 +6084,681 @@
   </cols>
   <sheetData>
     <row r="1" ht="15.75" spans="1:11">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2" t="s">
+      <c r="B1" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="G1" s="8"/>
+      <c r="H1" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" ht="15.75" spans="1:11">
+      <c r="A2" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="8"/>
+      <c r="F2" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="I2" s="15"/>
+      <c r="J2" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K2" s="8"/>
+    </row>
+    <row r="3" ht="15.75" spans="1:11">
+      <c r="A3" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="21"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="J3" s="8"/>
+      <c r="K3" s="8"/>
+    </row>
+    <row r="4" ht="30" spans="1:11">
+      <c r="A4" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="F4" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="H4" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="I4" s="23" t="s">
+        <v>38</v>
+      </c>
+      <c r="J4" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="K4" s="23" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" ht="30" spans="1:11">
+      <c r="A5" s="13"/>
+      <c r="B5" s="14">
+        <v>10</v>
+      </c>
+      <c r="C5" s="15">
+        <v>0.01</v>
+      </c>
+      <c r="D5" s="15">
+        <v>0.01</v>
+      </c>
+      <c r="E5" s="25" t="s">
+        <v>56</v>
+      </c>
+      <c r="F5" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="G5" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="H5" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="I5" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="J5" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="K5" s="21" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="6" ht="29.25" spans="1:11">
+      <c r="A6" s="16"/>
+      <c r="B6" s="14">
+        <v>11</v>
+      </c>
+      <c r="C6" s="15">
+        <v>0.1</v>
+      </c>
+      <c r="D6" s="15">
+        <v>0.1</v>
+      </c>
+      <c r="E6" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="F6" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="G6" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="H6" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="I6" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="J6" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="K6" s="21" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="7" ht="28.5" spans="1:11">
+      <c r="A7" s="17"/>
+      <c r="B7" s="14">
+        <v>12</v>
+      </c>
+      <c r="C7" s="15">
+        <v>1</v>
+      </c>
+      <c r="D7" s="15">
+        <v>1</v>
+      </c>
+      <c r="E7" s="25" t="s">
+        <v>71</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="G7" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="H7" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="I7" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="J7" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="K7" s="21" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="8" ht="29.25" spans="1:11">
+      <c r="A8" s="18"/>
+      <c r="B8" s="14">
+        <v>13</v>
+      </c>
+      <c r="C8" s="15">
+        <v>10</v>
+      </c>
+      <c r="D8" s="15">
+        <v>10</v>
+      </c>
+      <c r="E8" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="F8" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="G8" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="H8" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="I8" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="J8" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="K8" s="21" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="9" ht="28.5" spans="1:11">
+      <c r="A9" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="B9" s="14">
+        <v>14</v>
+      </c>
+      <c r="C9" s="20">
         <v>100</v>
       </c>
-      <c r="G1" s="2"/>
-      <c r="H1" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" ht="15.75" spans="1:11">
-      <c r="A2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="2"/>
-      <c r="F2" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="G2" s="2" t="s">
+      <c r="D9" s="20">
+        <v>100</v>
+      </c>
+      <c r="E9" s="26" t="s">
+        <v>76</v>
+      </c>
+      <c r="F9" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="G9" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="H9" s="27" t="s">
+        <v>85</v>
+      </c>
+      <c r="I9" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="J9" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="K9" s="28" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="10" ht="27.75" spans="1:11">
+      <c r="A10" s="16"/>
+      <c r="B10" s="14">
+        <v>15</v>
+      </c>
+      <c r="C10" s="15">
+        <v>100</v>
+      </c>
+      <c r="D10" s="15">
+        <v>100</v>
+      </c>
+      <c r="E10" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="F10" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="G10" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="H10" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="I10" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="J10" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="K10" s="29" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="11" customFormat="1" ht="28.5" spans="1:11">
+      <c r="A11" s="16"/>
+      <c r="B11" s="14">
+        <v>11</v>
+      </c>
+      <c r="C11" s="15">
+        <v>0.1</v>
+      </c>
+      <c r="D11" s="15">
+        <v>0.1</v>
+      </c>
+      <c r="E11" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="F11" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="G11" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="H11" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="I11" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="J11" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="K11" s="21" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="12" customFormat="1" ht="28.5" spans="1:11">
+      <c r="A12" s="17"/>
+      <c r="B12" s="14">
         <v>12</v>
       </c>
-      <c r="H2" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="I2" s="9"/>
-      <c r="J2" s="2" t="s">
+      <c r="C12" s="15">
+        <v>1</v>
+      </c>
+      <c r="D12" s="15">
+        <v>1</v>
+      </c>
+      <c r="E12" s="25" t="s">
+        <v>71</v>
+      </c>
+      <c r="F12" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="G12" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="H12" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="I12" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="J12" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="K12" s="21" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="13" customFormat="1" ht="28.5" spans="1:11">
+      <c r="A13" s="18"/>
+      <c r="B13" s="14">
+        <v>13</v>
+      </c>
+      <c r="C13" s="15">
+        <v>10</v>
+      </c>
+      <c r="D13" s="15">
+        <v>10</v>
+      </c>
+      <c r="E13" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="F13" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="G13" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="H13" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="I13" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="J13" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="K13" s="21" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="14" customFormat="1" ht="28.5" spans="1:11">
+      <c r="A14" s="16"/>
+      <c r="B14" s="14">
+        <v>11</v>
+      </c>
+      <c r="C14" s="15">
+        <v>0.1</v>
+      </c>
+      <c r="D14" s="15">
+        <v>0.1</v>
+      </c>
+      <c r="E14" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="F14" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="G14" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="H14" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="I14" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="J14" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="K14" s="21" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="15" customFormat="1" ht="28.5" spans="1:11">
+      <c r="A15" s="17"/>
+      <c r="B15" s="14">
+        <v>12</v>
+      </c>
+      <c r="C15" s="15">
+        <v>1</v>
+      </c>
+      <c r="D15" s="15">
+        <v>1</v>
+      </c>
+      <c r="E15" s="25" t="s">
+        <v>71</v>
+      </c>
+      <c r="F15" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="G15" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="H15" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="I15" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="J15" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="K15" s="21" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="16" customFormat="1" ht="28.5" spans="1:11">
+      <c r="A16" s="18"/>
+      <c r="B16" s="14">
+        <v>13</v>
+      </c>
+      <c r="C16" s="15">
+        <v>10</v>
+      </c>
+      <c r="D16" s="15">
+        <v>10</v>
+      </c>
+      <c r="E16" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="F16" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="G16" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="H16" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="I16" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="J16" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="K16" s="21" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="17" customFormat="1" ht="28.5" spans="1:11">
+      <c r="A17" s="17"/>
+      <c r="B17" s="14">
+        <v>12</v>
+      </c>
+      <c r="C17" s="15">
+        <v>1</v>
+      </c>
+      <c r="D17" s="15">
+        <v>1</v>
+      </c>
+      <c r="E17" s="25" t="s">
+        <v>71</v>
+      </c>
+      <c r="F17" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="G17" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="H17" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="I17" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="J17" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="K17" s="21" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="18" customFormat="1" ht="29.25" spans="1:11">
+      <c r="A18" s="18"/>
+      <c r="B18" s="14">
+        <v>13</v>
+      </c>
+      <c r="C18" s="15">
+        <v>10</v>
+      </c>
+      <c r="D18" s="15">
+        <v>10</v>
+      </c>
+      <c r="E18" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="F18" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="G18" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="H18" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="I18" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="J18" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="K18" s="21" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="19" customFormat="1" ht="28.5" spans="1:11">
+      <c r="A19" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="B19" s="14">
         <v>14</v>
       </c>
-      <c r="K2" s="2"/>
-    </row>
-    <row r="3" ht="15.75" spans="1:11">
-      <c r="A3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="I3" s="2" t="s">
+      <c r="C19" s="20">
+        <v>100</v>
+      </c>
+      <c r="D19" s="20">
+        <v>100</v>
+      </c>
+      <c r="E19" s="26" t="s">
+        <v>76</v>
+      </c>
+      <c r="F19" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="G19" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="H19" s="27" t="s">
+        <v>85</v>
+      </c>
+      <c r="I19" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="J19" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="K19" s="28" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="20" customFormat="1" ht="27.75" spans="1:11">
+      <c r="A20" s="16"/>
+      <c r="B20" s="14">
         <v>15</v>
       </c>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-    </row>
-    <row r="4" ht="30" spans="1:11">
-      <c r="A4" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="E4" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="F4" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="H4" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="I4" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="J4" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="K4" s="17" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="5" ht="30" spans="1:11">
-      <c r="A5" s="7"/>
-      <c r="B5" s="8">
-        <v>10</v>
-      </c>
-      <c r="C5" s="9">
-        <v>0.01</v>
-      </c>
-      <c r="D5" s="9">
-        <v>0.01</v>
-      </c>
-      <c r="E5" s="19" t="s">
-        <v>53</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="H5" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="I5" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="J5" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="K5" s="15" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="6" ht="29.25" spans="1:11">
-      <c r="A6" s="10"/>
-      <c r="B6" s="8">
+      <c r="C20" s="15">
+        <v>100</v>
+      </c>
+      <c r="D20" s="15">
+        <v>100</v>
+      </c>
+      <c r="E20" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="F20" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="G20" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="H20" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="I20" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="J20" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="K20" s="29" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="21" customFormat="1" ht="28.5" spans="1:11">
+      <c r="A21" s="16"/>
+      <c r="B21" s="14">
         <v>11</v>
       </c>
-      <c r="C6" s="9">
+      <c r="C21" s="15">
         <v>0.1</v>
       </c>
-      <c r="D6" s="9">
+      <c r="D21" s="15">
         <v>0.1</v>
       </c>
-      <c r="E6" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="F6" s="9" t="s">
+      <c r="E21" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="F21" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="G21" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="H21" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="I21" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="J21" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="K21" s="21" t="s">
         <v>63</v>
-      </c>
-      <c r="G6" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="H6" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="I6" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="J6" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="K6" s="15" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="7" ht="28.5" spans="1:11">
-      <c r="A7" s="11"/>
-      <c r="B7" s="8">
-        <v>12</v>
-      </c>
-      <c r="C7" s="9">
-        <v>1</v>
-      </c>
-      <c r="D7" s="9">
-        <v>1</v>
-      </c>
-      <c r="E7" s="19" t="s">
-        <v>68</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="H7" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="I7" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="J7" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="K7" s="15" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="8" ht="29.25" spans="1:11">
-      <c r="A8" s="12"/>
-      <c r="B8" s="8">
-        <v>13</v>
-      </c>
-      <c r="C8" s="9">
-        <v>10</v>
-      </c>
-      <c r="D8" s="9">
-        <v>10</v>
-      </c>
-      <c r="E8" s="19" t="s">
-        <v>73</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="G8" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="H8" s="15" t="s">
-        <v>76</v>
-      </c>
-      <c r="I8" s="15" t="s">
-        <v>78</v>
-      </c>
-      <c r="J8" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="K8" s="15" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="9" ht="28.5" spans="1:11">
-      <c r="A9" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="B9" s="8">
-        <v>14</v>
-      </c>
-      <c r="C9" s="14">
-        <v>100</v>
-      </c>
-      <c r="D9" s="14">
-        <v>100</v>
-      </c>
-      <c r="E9" s="20" t="s">
-        <v>73</v>
-      </c>
-      <c r="F9" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="G9" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="H9" s="21" t="s">
-        <v>82</v>
-      </c>
-      <c r="I9" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="J9" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="K9" s="22" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="10" ht="27.75" spans="1:11">
-      <c r="A10" s="10"/>
-      <c r="B10" s="8">
-        <v>15</v>
-      </c>
-      <c r="C10" s="9">
-        <v>100</v>
-      </c>
-      <c r="D10" s="9">
-        <v>100</v>
-      </c>
-      <c r="E10" s="19" t="s">
-        <v>73</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="H10" s="15" t="s">
-        <v>82</v>
-      </c>
-      <c r="I10" s="15" t="s">
-        <v>78</v>
-      </c>
-      <c r="J10" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K10" s="23" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="11" customFormat="1" ht="28.5" spans="1:11">
-      <c r="A11" s="10"/>
-      <c r="B11" s="8">
-        <v>11</v>
-      </c>
-      <c r="C11" s="9">
-        <v>0.1</v>
-      </c>
-      <c r="D11" s="9">
-        <v>0.1</v>
-      </c>
-      <c r="E11" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="G11" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="H11" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="I11" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="J11" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="K11" s="15" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="12" customFormat="1" ht="28.5" spans="1:11">
-      <c r="A12" s="11"/>
-      <c r="B12" s="8">
-        <v>12</v>
-      </c>
-      <c r="C12" s="9">
-        <v>1</v>
-      </c>
-      <c r="D12" s="9">
-        <v>1</v>
-      </c>
-      <c r="E12" s="19" t="s">
-        <v>68</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="G12" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="H12" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="I12" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="J12" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="K12" s="15" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="13" customFormat="1" ht="28.5" spans="1:11">
-      <c r="A13" s="12"/>
-      <c r="B13" s="8">
-        <v>13</v>
-      </c>
-      <c r="C13" s="9">
-        <v>10</v>
-      </c>
-      <c r="D13" s="9">
-        <v>10</v>
-      </c>
-      <c r="E13" s="19" t="s">
-        <v>73</v>
-      </c>
-      <c r="F13" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="G13" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="H13" s="15" t="s">
-        <v>76</v>
-      </c>
-      <c r="I13" s="15" t="s">
-        <v>78</v>
-      </c>
-      <c r="J13" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="K13" s="15" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="14" customFormat="1" ht="28.5" spans="1:11">
-      <c r="A14" s="10"/>
-      <c r="B14" s="8">
-        <v>11</v>
-      </c>
-      <c r="C14" s="9">
-        <v>0.1</v>
-      </c>
-      <c r="D14" s="9">
-        <v>0.1</v>
-      </c>
-      <c r="E14" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="F14" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="G14" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="H14" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="I14" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="J14" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="K14" s="15" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="15" customFormat="1" ht="28.5" spans="1:11">
-      <c r="A15" s="11"/>
-      <c r="B15" s="8">
-        <v>12</v>
-      </c>
-      <c r="C15" s="9">
-        <v>1</v>
-      </c>
-      <c r="D15" s="9">
-        <v>1</v>
-      </c>
-      <c r="E15" s="19" t="s">
-        <v>68</v>
-      </c>
-      <c r="F15" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="G15" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="H15" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="I15" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="J15" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="K15" s="15" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="16" customFormat="1" ht="28.5" spans="1:11">
-      <c r="A16" s="12"/>
-      <c r="B16" s="8">
-        <v>13</v>
-      </c>
-      <c r="C16" s="9">
-        <v>10</v>
-      </c>
-      <c r="D16" s="9">
-        <v>10</v>
-      </c>
-      <c r="E16" s="19" t="s">
-        <v>73</v>
-      </c>
-      <c r="F16" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="G16" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="H16" s="15" t="s">
-        <v>76</v>
-      </c>
-      <c r="I16" s="15" t="s">
-        <v>78</v>
-      </c>
-      <c r="J16" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="K16" s="15" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="17" customFormat="1" ht="28.5" spans="1:11">
-      <c r="A17" s="11"/>
-      <c r="B17" s="8">
-        <v>12</v>
-      </c>
-      <c r="C17" s="9">
-        <v>1</v>
-      </c>
-      <c r="D17" s="9">
-        <v>1</v>
-      </c>
-      <c r="E17" s="19" t="s">
-        <v>68</v>
-      </c>
-      <c r="F17" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="G17" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="H17" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="I17" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="J17" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="K17" s="15" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="18" customFormat="1" ht="29.25" spans="1:11">
-      <c r="A18" s="12"/>
-      <c r="B18" s="8">
-        <v>13</v>
-      </c>
-      <c r="C18" s="9">
-        <v>10</v>
-      </c>
-      <c r="D18" s="9">
-        <v>10</v>
-      </c>
-      <c r="E18" s="19" t="s">
-        <v>73</v>
-      </c>
-      <c r="F18" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="G18" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="H18" s="15" t="s">
-        <v>76</v>
-      </c>
-      <c r="I18" s="15" t="s">
-        <v>78</v>
-      </c>
-      <c r="J18" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="K18" s="15" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="19" customFormat="1" ht="28.5" spans="1:11">
-      <c r="A19" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="B19" s="8">
-        <v>14</v>
-      </c>
-      <c r="C19" s="14">
-        <v>100</v>
-      </c>
-      <c r="D19" s="14">
-        <v>100</v>
-      </c>
-      <c r="E19" s="20" t="s">
-        <v>73</v>
-      </c>
-      <c r="F19" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="G19" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="H19" s="21" t="s">
-        <v>82</v>
-      </c>
-      <c r="I19" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="J19" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="K19" s="22" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="20" customFormat="1" ht="27.75" spans="1:11">
-      <c r="A20" s="10"/>
-      <c r="B20" s="8">
-        <v>15</v>
-      </c>
-      <c r="C20" s="9">
-        <v>100</v>
-      </c>
-      <c r="D20" s="9">
-        <v>100</v>
-      </c>
-      <c r="E20" s="19" t="s">
-        <v>73</v>
-      </c>
-      <c r="F20" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="G20" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="H20" s="15" t="s">
-        <v>82</v>
-      </c>
-      <c r="I20" s="15" t="s">
-        <v>78</v>
-      </c>
-      <c r="J20" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K20" s="23" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="21" customFormat="1" ht="28.5" spans="1:11">
-      <c r="A21" s="10"/>
-      <c r="B21" s="8">
-        <v>11</v>
-      </c>
-      <c r="C21" s="9">
-        <v>0.1</v>
-      </c>
-      <c r="D21" s="9">
-        <v>0.1</v>
-      </c>
-      <c r="E21" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="F21" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="G21" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="H21" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="I21" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="J21" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="K21" s="15" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="22" ht="68" customHeight="1" spans="1:1">
       <c r="A22" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -6540,684 +6810,684 @@
   <sheetData>
     <row r="15" ht="15"/>
     <row r="16" ht="15.75" spans="5:15">
-      <c r="E16" s="1" t="s">
+      <c r="E16" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="F16" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2" t="s">
+      <c r="F16" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="J16" s="2" t="s">
+      <c r="J16" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="K16" s="8"/>
+      <c r="L16" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="M16" s="15"/>
+      <c r="N16" s="15"/>
+      <c r="O16" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" ht="15.75" spans="5:15">
+      <c r="E17" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="I17" s="8"/>
+      <c r="J17" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="K17" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="L17" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="M17" s="15"/>
+      <c r="N17" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="O17" s="8"/>
+    </row>
+    <row r="18" ht="15.75" spans="5:15">
+      <c r="E18" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="8"/>
+      <c r="J18" s="21"/>
+      <c r="K18" s="8"/>
+      <c r="L18" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="M18" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="N18" s="8"/>
+      <c r="O18" s="8"/>
+    </row>
+    <row r="19" ht="15.75" spans="5:15">
+      <c r="E19" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="G19" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="H19" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="I19" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="J19" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="K19" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="L19" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="M19" s="23" t="s">
+        <v>38</v>
+      </c>
+      <c r="N19" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="O19" s="23" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="20" ht="15.75" spans="5:15">
+      <c r="E20" s="13"/>
+      <c r="F20" s="14">
         <v>100</v>
       </c>
-      <c r="K16" s="2"/>
-      <c r="L16" s="9" t="s">
+      <c r="G20" s="15">
+        <v>0.01</v>
+      </c>
+      <c r="H20" s="15">
+        <v>0.01</v>
+      </c>
+      <c r="I20" s="25" t="s">
+        <v>56</v>
+      </c>
+      <c r="J20" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="K20" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="L20" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="M20" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="N20" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="O20" s="21" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="21" ht="15" spans="5:15">
+      <c r="E21" s="16"/>
+      <c r="F21" s="14">
         <v>101</v>
       </c>
-      <c r="M16" s="9"/>
-      <c r="N16" s="9"/>
-      <c r="O16" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" ht="15.75" spans="5:15">
-      <c r="E17" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="I17" s="2"/>
-      <c r="J17" s="15" t="s">
+      <c r="G21" s="15">
+        <v>0.1</v>
+      </c>
+      <c r="H21" s="15">
+        <v>0.1</v>
+      </c>
+      <c r="I21" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="J21" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="K21" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="L21" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="M21" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="N21" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="O21" s="21" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="22" spans="5:15">
+      <c r="E22" s="17"/>
+      <c r="F22" s="14">
         <v>102</v>
       </c>
-      <c r="K17" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="L17" s="9" t="s">
+      <c r="G22" s="15">
+        <v>1</v>
+      </c>
+      <c r="H22" s="15">
+        <v>1</v>
+      </c>
+      <c r="I22" s="25" t="s">
+        <v>71</v>
+      </c>
+      <c r="J22" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="K22" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="L22" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="M22" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="N22" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="O22" s="21" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="23" ht="15" spans="5:15">
+      <c r="E23" s="18"/>
+      <c r="F23" s="14">
         <v>103</v>
       </c>
-      <c r="M17" s="9"/>
-      <c r="N17" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="O17" s="2"/>
-    </row>
-    <row r="18" ht="15.75" spans="5:15">
-      <c r="E18" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="15"/>
-      <c r="K18" s="2"/>
-      <c r="L18" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="M18" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="N18" s="2"/>
-      <c r="O18" s="2"/>
-    </row>
-    <row r="19" ht="15.75" spans="5:15">
-      <c r="E19" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="H19" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="I19" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="J19" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="K19" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="L19" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="M19" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="N19" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="O19" s="17" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="20" ht="15.75" spans="5:15">
-      <c r="E20" s="7"/>
-      <c r="F20" s="8">
+      <c r="G23" s="15">
+        <v>10</v>
+      </c>
+      <c r="H23" s="15">
+        <v>10</v>
+      </c>
+      <c r="I23" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="J23" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="K23" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="L23" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="M23" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="N23" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="O23" s="21" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="24" ht="15.75" spans="5:15">
+      <c r="E24" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="F24" s="14">
+        <v>104</v>
+      </c>
+      <c r="G24" s="20">
         <v>100</v>
       </c>
-      <c r="G20" s="9">
-        <v>0.01</v>
-      </c>
-      <c r="H20" s="9">
-        <v>0.01</v>
-      </c>
-      <c r="I20" s="19" t="s">
-        <v>53</v>
-      </c>
-      <c r="J20" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="K20" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="L20" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="M20" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="N20" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="O20" s="15" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="21" ht="15" spans="5:15">
-      <c r="E21" s="10"/>
-      <c r="F21" s="8">
-        <v>101</v>
-      </c>
-      <c r="G21" s="9">
+      <c r="H24" s="20">
+        <v>100</v>
+      </c>
+      <c r="I24" s="26" t="s">
+        <v>76</v>
+      </c>
+      <c r="J24" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="K24" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="L24" s="27" t="s">
+        <v>85</v>
+      </c>
+      <c r="M24" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="N24" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="O24" s="28" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="25" ht="15" spans="5:15">
+      <c r="E25" s="16"/>
+      <c r="F25" s="14">
+        <v>105</v>
+      </c>
+      <c r="G25" s="15">
+        <v>100</v>
+      </c>
+      <c r="H25" s="15">
+        <v>100</v>
+      </c>
+      <c r="I25" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="J25" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="K25" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="L25" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="M25" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="N25" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="O25" s="29" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="26" spans="5:15">
+      <c r="E26" s="16"/>
+      <c r="F26" s="14">
+        <v>106</v>
+      </c>
+      <c r="G26" s="15">
         <v>0.1</v>
       </c>
-      <c r="H21" s="9">
+      <c r="H26" s="15">
         <v>0.1</v>
       </c>
-      <c r="I21" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="J21" s="9" t="s">
+      <c r="I26" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="J26" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="K26" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="L26" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="M26" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="N26" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="O26" s="21" t="s">
         <v>63</v>
       </c>
-      <c r="K21" s="9" t="s">
+    </row>
+    <row r="27" spans="5:15">
+      <c r="E27" s="17"/>
+      <c r="F27" s="14">
+        <v>107</v>
+      </c>
+      <c r="G27" s="15">
+        <v>1</v>
+      </c>
+      <c r="H27" s="15">
+        <v>1</v>
+      </c>
+      <c r="I27" s="25" t="s">
+        <v>71</v>
+      </c>
+      <c r="J27" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="K27" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="L27" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="M27" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="N27" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="O27" s="21" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="28" spans="5:15">
+      <c r="E28" s="18"/>
+      <c r="F28" s="14">
+        <v>108</v>
+      </c>
+      <c r="G28" s="15">
+        <v>10</v>
+      </c>
+      <c r="H28" s="15">
+        <v>10</v>
+      </c>
+      <c r="I28" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="J28" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="K28" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="L28" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="M28" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="N28" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="O28" s="21" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="29" spans="5:15">
+      <c r="E29" s="16"/>
+      <c r="F29" s="14">
+        <v>109</v>
+      </c>
+      <c r="G29" s="15">
+        <v>0.1</v>
+      </c>
+      <c r="H29" s="15">
+        <v>0.1</v>
+      </c>
+      <c r="I29" s="25" t="s">
         <v>64</v>
       </c>
-      <c r="L21" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="M21" s="15" t="s">
+      <c r="J29" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="K29" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="N21" s="9" t="s">
+      <c r="L29" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="M29" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="N29" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="O29" s="21" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="30" spans="5:15">
+      <c r="E30" s="17"/>
+      <c r="F30" s="14">
+        <v>110</v>
+      </c>
+      <c r="G30" s="15">
+        <v>1</v>
+      </c>
+      <c r="H30" s="15">
+        <v>1</v>
+      </c>
+      <c r="I30" s="25" t="s">
+        <v>71</v>
+      </c>
+      <c r="J30" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="K30" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="L30" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="M30" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="N30" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="O30" s="21" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="31" spans="5:15">
+      <c r="E31" s="18"/>
+      <c r="F31" s="14">
+        <v>111</v>
+      </c>
+      <c r="G31" s="15">
+        <v>10</v>
+      </c>
+      <c r="H31" s="15">
+        <v>10</v>
+      </c>
+      <c r="I31" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="J31" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="K31" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="L31" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="M31" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="N31" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="O31" s="21" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="32" spans="5:15">
+      <c r="E32" s="17"/>
+      <c r="F32" s="14">
+        <v>112</v>
+      </c>
+      <c r="G32" s="15">
+        <v>1</v>
+      </c>
+      <c r="H32" s="15">
+        <v>1</v>
+      </c>
+      <c r="I32" s="25" t="s">
+        <v>71</v>
+      </c>
+      <c r="J32" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="K32" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="L32" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="M32" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="N32" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="O32" s="21" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="33" ht="15" spans="5:15">
+      <c r="E33" s="18"/>
+      <c r="F33" s="14">
+        <v>113</v>
+      </c>
+      <c r="G33" s="15">
+        <v>10</v>
+      </c>
+      <c r="H33" s="15">
+        <v>10</v>
+      </c>
+      <c r="I33" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="J33" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="K33" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="L33" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="M33" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="N33" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="O33" s="21" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="34" ht="15.75" spans="5:15">
+      <c r="E34" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="F34" s="14">
+        <v>114</v>
+      </c>
+      <c r="G34" s="20">
+        <v>100</v>
+      </c>
+      <c r="H34" s="20">
+        <v>100</v>
+      </c>
+      <c r="I34" s="26" t="s">
+        <v>76</v>
+      </c>
+      <c r="J34" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="K34" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="L34" s="27" t="s">
+        <v>85</v>
+      </c>
+      <c r="M34" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="N34" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="O34" s="28" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="35" ht="15" spans="5:15">
+      <c r="E35" s="16"/>
+      <c r="F35" s="14">
+        <v>115</v>
+      </c>
+      <c r="G35" s="15">
+        <v>100</v>
+      </c>
+      <c r="H35" s="15">
+        <v>100</v>
+      </c>
+      <c r="I35" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="J35" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="K35" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="L35" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="M35" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="N35" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="O35" s="29" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="36" spans="5:15">
+      <c r="E36" s="16"/>
+      <c r="F36" s="14">
+        <v>116</v>
+      </c>
+      <c r="G36" s="15">
+        <v>0.1</v>
+      </c>
+      <c r="H36" s="15">
+        <v>0.1</v>
+      </c>
+      <c r="I36" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="J36" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="O21" s="15" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="22" spans="5:15">
-      <c r="E22" s="11"/>
-      <c r="F22" s="8">
-        <v>102</v>
-      </c>
-      <c r="G22" s="9">
-        <v>1</v>
-      </c>
-      <c r="H22" s="9">
-        <v>1</v>
-      </c>
-      <c r="I22" s="19" t="s">
+      <c r="K36" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="L36" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="J22" s="9" t="s">
+      <c r="M36" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="N36" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="K22" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="L22" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="M22" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="N22" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="O22" s="15" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="23" ht="15" spans="5:15">
-      <c r="E23" s="12"/>
-      <c r="F23" s="8">
-        <v>103</v>
-      </c>
-      <c r="G23" s="9">
-        <v>10</v>
-      </c>
-      <c r="H23" s="9">
-        <v>10</v>
-      </c>
-      <c r="I23" s="19" t="s">
-        <v>73</v>
-      </c>
-      <c r="J23" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="K23" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="L23" s="15" t="s">
-        <v>76</v>
-      </c>
-      <c r="M23" s="15" t="s">
-        <v>78</v>
-      </c>
-      <c r="N23" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="O23" s="15" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="24" ht="15.75" spans="5:15">
-      <c r="E24" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="F24" s="8">
-        <v>104</v>
-      </c>
-      <c r="G24" s="14">
-        <v>100</v>
-      </c>
-      <c r="H24" s="14">
-        <v>100</v>
-      </c>
-      <c r="I24" s="20" t="s">
-        <v>73</v>
-      </c>
-      <c r="J24" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="K24" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="L24" s="21" t="s">
-        <v>82</v>
-      </c>
-      <c r="M24" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="N24" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="O24" s="22" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="25" ht="15" spans="5:15">
-      <c r="E25" s="10"/>
-      <c r="F25" s="8">
-        <v>105</v>
-      </c>
-      <c r="G25" s="9">
-        <v>100</v>
-      </c>
-      <c r="H25" s="9">
-        <v>100</v>
-      </c>
-      <c r="I25" s="19" t="s">
-        <v>73</v>
-      </c>
-      <c r="J25" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="K25" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="L25" s="15" t="s">
-        <v>82</v>
-      </c>
-      <c r="M25" s="15" t="s">
-        <v>78</v>
-      </c>
-      <c r="N25" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="O25" s="23" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="26" spans="5:15">
-      <c r="E26" s="10"/>
-      <c r="F26" s="8">
-        <v>106</v>
-      </c>
-      <c r="G26" s="9">
-        <v>0.1</v>
-      </c>
-      <c r="H26" s="9">
-        <v>0.1</v>
-      </c>
-      <c r="I26" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="J26" s="9" t="s">
+      <c r="O36" s="21" t="s">
         <v>63</v>
-      </c>
-      <c r="K26" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="L26" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="M26" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="N26" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="O26" s="15" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="27" spans="5:15">
-      <c r="E27" s="11"/>
-      <c r="F27" s="8">
-        <v>107</v>
-      </c>
-      <c r="G27" s="9">
-        <v>1</v>
-      </c>
-      <c r="H27" s="9">
-        <v>1</v>
-      </c>
-      <c r="I27" s="19" t="s">
-        <v>68</v>
-      </c>
-      <c r="J27" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="K27" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="L27" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="M27" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="N27" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="O27" s="15" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="28" spans="5:15">
-      <c r="E28" s="12"/>
-      <c r="F28" s="8">
-        <v>108</v>
-      </c>
-      <c r="G28" s="9">
-        <v>10</v>
-      </c>
-      <c r="H28" s="9">
-        <v>10</v>
-      </c>
-      <c r="I28" s="19" t="s">
-        <v>73</v>
-      </c>
-      <c r="J28" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="K28" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="L28" s="15" t="s">
-        <v>76</v>
-      </c>
-      <c r="M28" s="15" t="s">
-        <v>78</v>
-      </c>
-      <c r="N28" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="O28" s="15" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="29" spans="5:15">
-      <c r="E29" s="10"/>
-      <c r="F29" s="8">
-        <v>109</v>
-      </c>
-      <c r="G29" s="9">
-        <v>0.1</v>
-      </c>
-      <c r="H29" s="9">
-        <v>0.1</v>
-      </c>
-      <c r="I29" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="J29" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="K29" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="L29" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="M29" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="N29" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="O29" s="15" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="30" spans="5:15">
-      <c r="E30" s="11"/>
-      <c r="F30" s="8">
-        <v>110</v>
-      </c>
-      <c r="G30" s="9">
-        <v>1</v>
-      </c>
-      <c r="H30" s="9">
-        <v>1</v>
-      </c>
-      <c r="I30" s="19" t="s">
-        <v>68</v>
-      </c>
-      <c r="J30" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="K30" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="L30" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="M30" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="N30" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="O30" s="15" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="31" spans="5:15">
-      <c r="E31" s="12"/>
-      <c r="F31" s="8">
-        <v>111</v>
-      </c>
-      <c r="G31" s="9">
-        <v>10</v>
-      </c>
-      <c r="H31" s="9">
-        <v>10</v>
-      </c>
-      <c r="I31" s="19" t="s">
-        <v>73</v>
-      </c>
-      <c r="J31" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="K31" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="L31" s="15" t="s">
-        <v>76</v>
-      </c>
-      <c r="M31" s="15" t="s">
-        <v>78</v>
-      </c>
-      <c r="N31" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="O31" s="15" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="32" spans="5:15">
-      <c r="E32" s="11"/>
-      <c r="F32" s="8">
-        <v>112</v>
-      </c>
-      <c r="G32" s="9">
-        <v>1</v>
-      </c>
-      <c r="H32" s="9">
-        <v>1</v>
-      </c>
-      <c r="I32" s="19" t="s">
-        <v>68</v>
-      </c>
-      <c r="J32" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="K32" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="L32" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="M32" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="N32" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="O32" s="15" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="33" ht="15" spans="5:15">
-      <c r="E33" s="12"/>
-      <c r="F33" s="8">
-        <v>113</v>
-      </c>
-      <c r="G33" s="9">
-        <v>10</v>
-      </c>
-      <c r="H33" s="9">
-        <v>10</v>
-      </c>
-      <c r="I33" s="19" t="s">
-        <v>73</v>
-      </c>
-      <c r="J33" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="K33" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="L33" s="15" t="s">
-        <v>76</v>
-      </c>
-      <c r="M33" s="15" t="s">
-        <v>78</v>
-      </c>
-      <c r="N33" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="O33" s="15" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="34" ht="15.75" spans="5:15">
-      <c r="E34" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="F34" s="8">
-        <v>114</v>
-      </c>
-      <c r="G34" s="14">
-        <v>100</v>
-      </c>
-      <c r="H34" s="14">
-        <v>100</v>
-      </c>
-      <c r="I34" s="20" t="s">
-        <v>73</v>
-      </c>
-      <c r="J34" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="K34" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="L34" s="21" t="s">
-        <v>82</v>
-      </c>
-      <c r="M34" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="N34" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="O34" s="22" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="35" ht="15" spans="5:15">
-      <c r="E35" s="10"/>
-      <c r="F35" s="8">
-        <v>115</v>
-      </c>
-      <c r="G35" s="9">
-        <v>100</v>
-      </c>
-      <c r="H35" s="9">
-        <v>100</v>
-      </c>
-      <c r="I35" s="19" t="s">
-        <v>73</v>
-      </c>
-      <c r="J35" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="K35" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="L35" s="15" t="s">
-        <v>82</v>
-      </c>
-      <c r="M35" s="15" t="s">
-        <v>78</v>
-      </c>
-      <c r="N35" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="O35" s="23" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="36" spans="5:15">
-      <c r="E36" s="10"/>
-      <c r="F36" s="8">
-        <v>116</v>
-      </c>
-      <c r="G36" s="9">
-        <v>0.1</v>
-      </c>
-      <c r="H36" s="9">
-        <v>0.1</v>
-      </c>
-      <c r="I36" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="J36" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="K36" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="L36" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="M36" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="N36" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="O36" s="15" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="39" spans="5:6">
       <c r="E39" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F39" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -7243,4 +7513,249 @@
   <drawing r:id="rId2"/>
   <legacyDrawing r:id="rId3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F20"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="1" width="9" style="1"/>
+    <col min="2" max="2" width="9.375" style="1"/>
+    <col min="3" max="3" width="12.5" style="1" customWidth="1"/>
+    <col min="4" max="4" width="36.25" style="1" customWidth="1"/>
+    <col min="5" max="5" width="15.875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="24.5" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:6">
+      <c r="A1" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+    </row>
+    <row r="2" s="1" customFormat="1" spans="1:6">
+      <c r="A2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" spans="1:6">
+      <c r="A3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="3"/>
+      <c r="C3" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+    </row>
+    <row r="4" s="1" customFormat="1" spans="1:6">
+      <c r="A4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" ht="40.5" spans="2:6">
+      <c r="B6" s="1">
+        <v>20260101</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" spans="1:5">
+      <c r="A13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" spans="1:5">
+      <c r="A14" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" spans="1:5">
+      <c r="A15" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" ht="16.5" spans="2:5">
+      <c r="B16" s="1">
+        <v>1</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="D16" s="1">
+        <v>1</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" ht="16.5" spans="2:5">
+      <c r="B17" s="1">
+        <v>2</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="D17" s="1">
+        <v>2</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" ht="16.5" spans="2:5">
+      <c r="B18" s="1">
+        <v>3</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="D18" s="1">
+        <v>3</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" ht="16.5" spans="2:5">
+      <c r="B19" s="1">
+        <v>4</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="D19" s="1">
+        <v>4</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="20" s="1" customFormat="1" ht="16.5" spans="2:4">
+      <c r="B20" s="1">
+        <v>5</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="D20" s="1">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
 </file>